--- a/results/Int Task Remove ACC -0.1/Linea_fi_all.xlsx
+++ b/results/Int Task Remove ACC -0.1/Linea_fi_all.xlsx
@@ -911,7 +911,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.00043624161073828603 +/- 0.0008362373016360414</t>
+          <t>0.00040268456375842644 +/- 0.000859479763413795</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.00040268456375842644 +/- 0.0009226662473065453</t>
+          <t>0.00040268456375842644 +/- 0.000859479763413795</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.012768910478834194 +/- 0.003469118598181802</t>
+          <t>0.012803608605135375 +/- 0.0034852190928764356</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.06161825726141079 +/- 0.005429539813662642</t>
+          <t>0.06158367911479945 +/- 0.0054900907146884625</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.0895228215767635 +/- 0.0051992702060493405</t>
+          <t>0.08948824343015216 +/- 0.005197775221054906</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.02313278008298758 +/- 0.004413152377346114</t>
+          <t>0.023167358229598922 +/- 0.0044010795509536</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.010868079289131893 +/- 0.002565731289012093</t>
+          <t>0.010833902939166074 +/- 0.0026164445721699467</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.028366370471633616 +/- 0.004821167457165367</t>
+          <t>0.0283321941216678 +/- 0.004822257547674454</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.03752563226247435 +/- 0.00670205106862899</t>
+          <t>0.03755980861244017 +/- 0.006657724905531838</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.03735475051264522 +/- 0.0038455608041930013</t>
+          <t>0.0373205741626794 +/- 0.0038991006690230075</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.0014695830485304206 +/- 0.001242158704400957</t>
+          <t>0.0015037593984962405 +/- 0.0012896761629605524</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.016649916247906217 +/- 0.002171360860716756</t>
+          <t>0.016683417085427154 +/- 0.0021906576514937096</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.01440536013400332 +/- 0.0038576908999624396</t>
+          <t>-0.014438860971524258 +/- 0.0038735139661739814</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.015738654650788574 +/- 0.004100196087364096</t>
+          <t>0.01570646926295466 +/- 0.004111171509967392</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0.15152880592211143 +/- 0.003221112585309751</t>
+          <t>0.15149662053427745 +/- 0.0031928488734964166</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.08850981654328938 +/- 0.0025383642295629654</t>
+          <t>0.0885420019311233 +/- 0.002536118702039509</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.010268780151619616 +/- 0.007098552722260509</t>
+          <t>0.010234321157822236 +/- 0.007098970901615228</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.00792556857339768 +/- 0.0017366785897111056</t>
+          <t>0.00792556857339768 +/- 0.0016525952871511668</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.003054187192118285 +/- 0.004083489969217984</t>
+          <t>0.003021346469622388 +/- 0.004035000999253253</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.0003612479474548902 +/- 0.0009224677770238487</t>
+          <t>0.0003284072249589931 +/- 0.0009053562398745586</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0067364746945899005 +/- 0.0032893213863960467</t>
+          <t>0.006771378708551512 +/- 0.0033046563011642953</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4926,14 +4926,14 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>0.05137870855148348 +/- 0.0032548811802791807</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>0.05141361256544508 +/- 0.0032219637978063978</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.05141361256544508 +/- 0.0032219637978063978</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>0.01162303664921469 +/- 0.002468333292598564</t>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.017626527050610873 +/- 0.00264096787965471</t>
+          <t>0.017661431064572485 +/- 0.0027090552058544166</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>-0.03106457242582896 +/- 0.002770420221010047</t>
+          <t>-0.031134380453752164 +/- 0.0027695405828799167</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="BC11" t="inlineStr">
         <is>
+          <t>-0.0006980802792320717 +/- 0.0007804774790575208</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
           <t>-0.0006631762652704709 +/- 0.0007718444812389547</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>-0.0006980802792320717 +/- 0.0007804774790575208</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
